--- a/tabtools/demo/demo_corrtab.xlsx
+++ b/tabtools/demo/demo_corrtab.xlsx
@@ -1410,7 +1410,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="221">
+  <borders count="227">
     <border>
       <left/>
       <right/>
@@ -1421,6 +1421,8 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -1928,475 +1930,479 @@
     <border/>
     <border/>
     <border/>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
     <border/>
     <border/>
     <border/>
@@ -2908,858 +2914,864 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="221">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0"/>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="155" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="157" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="163" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="171" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="81" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="173" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="175" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="176" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="177" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="179" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="180" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="181" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="186" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="188" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="190" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="191" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="192" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="193" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="194" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="195" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="175" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="188" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="190" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="191" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="192" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="193" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="194" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="195" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="196" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="196" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="197" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="197" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="198" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="198" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="199" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="200" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="201" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="202" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="203" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="204" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="205" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="206" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="207" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="208" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="209" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="210" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="211" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="146" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="147" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" xfId="0"/>
-    <xf numFmtId="0" fontId="213" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="215" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="217" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="219" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="221" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="223" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="225" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="227" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="229" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="231" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="233" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="235" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="237" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="239" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="241" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="243" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="245" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="247" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="249" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="251" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="253" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="255" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="257" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="259" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="261" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="263" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="265" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="267" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="269" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="271" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="273" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="274" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="199" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="201" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="202" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="203" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="204" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="205" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="206" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="207" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="208" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="209" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="211" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="150" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="151" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="152" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="153" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="154" xfId="0"/>
+    <xf numFmtId="0" fontId="213" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="215" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="217" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="219" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="221" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="223" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="225" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="227" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="229" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="235" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="237" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="239" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="241" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="243" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="245" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="247" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="249" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="251" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="253" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="255" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="259" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="261" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="263" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="265" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="267" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="269" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="271" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="273" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="274" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="275" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="275" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="276" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="276" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="277" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="278" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="279" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="280" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="281" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="282" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="283" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="284" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="286" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="288" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="290" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="292" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="293" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="294" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="295" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="296" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="297" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="277" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="278" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="279" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="280" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="281" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="282" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="283" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="284" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="286" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="288" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="290" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="292" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="293" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="294" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="295" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="296" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="297" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="298" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="298" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="299" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="299" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="300" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="300" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="301" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="302" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="303" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="304" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="305" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="306" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="307" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="308" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="309" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="310" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="311" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="312" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="313" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="314" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="301" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="302" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="303" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="304" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="305" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="307" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="309" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="310" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="311" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="313" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="315" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="315" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="316" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="316" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="318" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="318" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="320" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="320" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3777,96 +3789,98 @@
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
     <col min="2" max="2" width="25.7109375" style="2" customWidth="true"/>
-    <col min="3" max="5" width="24.7109375" style="3" customWidth="true"/>
+    <col min="3" max="3" width="24.7109375" style="3" customWidth="true"/>
+    <col min="4" max="4" width="24.7109375" style="4" customWidth="true"/>
+    <col min="5" max="5" width="24.7109375" style="5" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="31" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="59" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="60" t="s">
+      <c r="E3" s="62" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="61" t="s">
+      <c r="C4" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="62" t="s">
+      <c r="D4" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="63" t="s">
+      <c r="E4" s="65" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="67" t="s">
+      <c r="B5" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="70" t="s">
+      <c r="E5" s="72" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="77" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="2"/>
@@ -3886,93 +3900,95 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="76" customWidth="true"/>
-    <col min="2" max="2" width="25.7109375" style="77" customWidth="true"/>
-    <col min="3" max="5" width="24.7109375" style="78" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="78" customWidth="true"/>
+    <col min="2" max="2" width="25.7109375" style="79" customWidth="true"/>
+    <col min="3" max="3" width="24.7109375" style="80" customWidth="true"/>
+    <col min="4" max="4" width="24.7109375" style="81" customWidth="true"/>
+    <col min="5" max="5" width="24.7109375" style="82" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="116" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="104" t="s">
+      <c r="C1" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="104" t="s">
+      <c r="D1" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="104" t="s">
+      <c r="E1" s="108" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="133" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="130" t="s">
+      <c r="C2" s="134" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="131" t="s">
+      <c r="D2" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="132" t="s">
+      <c r="E2" s="136" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="89" t="s">
+      <c r="A3" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="90" t="s">
+      <c r="B3" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="133" t="s">
+      <c r="C3" s="137" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="134" t="s">
+      <c r="D3" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="135" t="s">
+      <c r="E3" s="139" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="C4" s="140" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="141" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="138" t="s">
+      <c r="E4" s="142" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="142" t="s">
+      <c r="B5" s="146" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="143" t="s">
+      <c r="C5" s="147" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="144" t="s">
+      <c r="D5" s="148" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="145" t="s">
+      <c r="E5" s="149" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3988,103 +4004,105 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="146" customWidth="true"/>
-    <col min="2" max="2" width="25.7109375" style="147" customWidth="true"/>
-    <col min="3" max="5" width="24.7109375" style="148" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="150" customWidth="true"/>
+    <col min="2" max="2" width="25.7109375" style="151" customWidth="true"/>
+    <col min="3" max="3" width="24.7109375" style="152" customWidth="true"/>
+    <col min="4" max="4" width="24.7109375" style="153" customWidth="true"/>
+    <col min="5" max="5" width="24.7109375" style="154" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="188" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="174" t="s">
+      <c r="B1" s="180" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="174" t="s">
+      <c r="C1" s="180" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="174" t="s">
+      <c r="D1" s="180" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="174" t="s">
+      <c r="E1" s="180" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="154" t="s">
+      <c r="A2" s="160" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="199" t="s">
+      <c r="B2" s="205" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="200" t="s">
+      <c r="C2" s="206" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="201" t="s">
+      <c r="D2" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="202" t="s">
+      <c r="E2" s="208" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="159" t="s">
+      <c r="A3" s="165" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="160" t="s">
+      <c r="B3" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="203" t="s">
+      <c r="C3" s="209" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="204" t="s">
+      <c r="D3" s="210" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="205" t="s">
+      <c r="E3" s="211" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="164" t="s">
+      <c r="A4" s="170" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="165" t="s">
+      <c r="B4" s="171" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="206" t="s">
+      <c r="C4" s="212" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="207" t="s">
+      <c r="D4" s="213" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="208" t="s">
+      <c r="E4" s="214" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="175" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="212" t="s">
+      <c r="B5" s="218" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="213" t="s">
+      <c r="C5" s="219" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="214" t="s">
+      <c r="D5" s="220" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="215" t="s">
+      <c r="E5" s="221" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="220" t="s">
+      <c r="B6" s="226" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="147"/>
-      <c r="D6" s="147"/>
-      <c r="E6" s="147"/>
+      <c r="C6" s="151"/>
+      <c r="D6" s="151"/>
+      <c r="E6" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/tabtools/demo/demo_corrtab.xlsx
+++ b/tabtools/demo/demo_corrtab.xlsx
@@ -38,7 +38,7 @@
     <t>-0.01</t>
   </si>
   <si>
-    <t>-0.00</t>
+    <t>0.00</t>
   </si>
   <si>
     <t>0.01</t>
@@ -50,10 +50,10 @@
     <t>Table 14. Spearman Rank Correlation Matrix</t>
   </si>
   <si>
-    <t>-0.00 (0.616)</t>
+    <t>0.00 (0.616)</t>
   </si>
   <si>
-    <t>-0.00 (0.807)</t>
+    <t>0.00 (0.807)</t>
   </si>
   <si>
     <t>0.01 (0.450)</t>

--- a/tabtools/demo/demo_corrtab.xlsx
+++ b/tabtools/demo/demo_corrtab.xlsx
@@ -44,7 +44,7 @@
     <t>0.01</t>
   </si>
   <si>
-    <t>* p&lt;.05, ** p&lt;.01, *** p&lt;.001</t>
+    <t>* p&lt;0.05, ** p&lt;0.01, *** p&lt;0.001</t>
   </si>
   <si>
     <t>Table 14. Spearman Rank Correlation Matrix</t>
